--- a/papers/paperlist.xlsx
+++ b/papers/paperlist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamabehiroyuki/Library/Mobile Documents/com~apple~CloudDocs/Graduation Research/GR2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hiroyuki\gr_avsr\papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAEB8E5-518F-684A-801F-043D20B9F8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73451391-2513-4824-B9CF-CC33C2FDF1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="600" windowWidth="28300" windowHeight="15740" xr2:uid="{D4213BA5-E86C-EC41-9D7E-E69E79C1F0C7}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{D4213BA5-E86C-EC41-9D7E-E69E79C1F0C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -316,7 +316,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -755,7 +755,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB58914-CBFC-D041-96CC-04516860249B}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="59" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="59" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.33203125" customWidth="1"/>
     <col min="3" max="3" width="65.5" customWidth="1"/>
@@ -763,7 +763,7 @@
     <col min="5" max="5" width="45.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="59" customHeight="1">
+    <row r="1" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>19</v>
       </c>
@@ -777,14 +777,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:5" ht="59" customHeight="1">
+    <row r="2" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="2:5" ht="59" customHeight="1">
+    <row r="3" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
@@ -793,7 +793,7 @@
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="2:5" ht="59" customHeight="1">
+    <row r="4" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
@@ -804,7 +804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="59" customHeight="1">
+    <row r="5" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
@@ -813,7 +813,7 @@
       </c>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="2:5" ht="59" customHeight="1">
+    <row r="6" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>19</v>
       </c>
@@ -825,14 +825,14 @@
       </c>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="2:5" ht="59" customHeight="1">
+    <row r="7" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="2:5" ht="59" customHeight="1">
+    <row r="8" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>19</v>
       </c>
@@ -846,7 +846,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="59" customHeight="1">
+    <row r="9" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>19</v>
       </c>
@@ -858,7 +858,7 @@
       </c>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="2:5" ht="59" customHeight="1">
+    <row r="10" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -869,7 +869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="59" customHeight="1">
+    <row r="11" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="8" t="s">
         <v>22</v>
       </c>
@@ -877,7 +877,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="59" customHeight="1">
+    <row r="12" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
@@ -885,7 +885,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="59" customHeight="1">
+    <row r="13" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -896,7 +896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="59" customHeight="1">
+    <row r="14" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>19</v>
       </c>
@@ -907,7 +907,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="59" customHeight="1">
+    <row r="15" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
@@ -918,7 +918,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="59" customHeight="1">
+    <row r="16" spans="2:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>19</v>
       </c>
@@ -929,7 +929,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="59" customHeight="1">
+    <row r="17" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>31</v>
       </c>
@@ -937,7 +937,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="59" customHeight="1">
+    <row r="18" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -951,7 +951,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="59" customHeight="1">
+    <row r="19" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>19</v>
       </c>
@@ -965,7 +965,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="59" customHeight="1">
+    <row r="20" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>55</v>
       </c>
@@ -973,7 +973,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="59" customHeight="1">
+    <row r="21" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>19</v>
       </c>
@@ -981,7 +981,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="59" customHeight="1">
+    <row r="22" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>42</v>
       </c>
@@ -989,7 +989,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="59" customHeight="1">
+    <row r="23" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>45</v>
       </c>
@@ -997,7 +997,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="59" customHeight="1">
+    <row r="24" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>54</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="59" customHeight="1">
+    <row r="25" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>53</v>
       </c>
@@ -1013,14 +1013,14 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="59" customHeight="1">
+    <row r="26" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:5" ht="59" customHeight="1">
+    <row r="27" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>51</v>
       </c>
